--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -146,18 +146,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -176,166 +176,166 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BENITEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>BENITEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>IVETTE</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
     <t>IAN URIEL</t>
   </si>
   <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
   </si>
 </sst>
 </file>
@@ -840,7 +840,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -849,13 +849,13 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -912,13 +912,13 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -944,7 +944,7 @@
         <v>-1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1018,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1027,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1090,13 +1090,13 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1122,7 +1122,7 @@
         <v>-1</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1185,7 +1185,7 @@
         <v>-1</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1211,7 +1211,7 @@
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1274,7 +1274,7 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1294,13 +1294,13 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>-1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1357,13 +1357,13 @@
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -1383,13 +1383,13 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1437,7 +1437,7 @@
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1446,13 +1446,13 @@
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1463,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -1472,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1526,7 +1526,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1535,13 +1535,13 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1552,7 +1552,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1561,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>-1</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1624,13 +1624,13 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>-1</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1650,13 +1650,13 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1713,13 +1713,13 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>-1</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
         <v>-1</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1802,13 +1802,13 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1819,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1828,13 +1828,13 @@
         <v>8</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>-1</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1882,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1891,13 +1891,13 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>-1</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1917,13 +1917,13 @@
         <v>9</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>-1</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1971,7 +1971,7 @@
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1980,13 +1980,13 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>-1</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2012,7 +2012,7 @@
         <v>-1</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2095,13 +2095,13 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2158,13 +2158,13 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>-1</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2175,7 +2175,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2184,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -2229,7 +2229,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2238,7 +2238,7 @@
         <v>7</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2330,7 +2330,7 @@
         <v>-1</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2341,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2350,13 +2350,13 @@
         <v>8</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2404,7 +2404,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2413,13 +2413,13 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2445,7 +2445,7 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2508,7 +2508,7 @@
         <v>-1</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2534,7 +2534,7 @@
         <v>-1</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2597,7 +2597,7 @@
         <v>-1</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2662,22 +2662,25 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.3</v>
+      </c>
       <c r="I2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2691,22 +2694,25 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.2</v>
+      </c>
       <c r="I3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2720,27 +2726,30 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>63.16</v>
+      </c>
+      <c r="G4">
+        <v>36.84</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>19</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2749,25 +2758,25 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2873,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2902,116 +2911,116 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>20330051920261</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920260</v>
+        <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920260</v>
+        <v>20330051920261</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B6" t="s">
         <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3022,39 +3031,39 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920261</v>
+        <v>20330051920264</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
@@ -3062,279 +3071,279 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B10" t="s">
         <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B12" t="s">
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920262</v>
+        <v>20330051920264</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920262</v>
+        <v>20330051920267</v>
       </c>
       <c r="B14" t="s">
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920262</v>
+        <v>20330051920267</v>
       </c>
       <c r="B15" t="s">
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920264</v>
+        <v>20330051920267</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920264</v>
+        <v>20330051920267</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920264</v>
+        <v>20330051920269</v>
       </c>
       <c r="B18" t="s">
         <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920264</v>
+        <v>20330051920270</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920264</v>
+        <v>20330051920270</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920264</v>
+        <v>20330051920271</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920264</v>
+        <v>20330051920271</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920267</v>
+        <v>20330051920272</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
@@ -3342,13 +3351,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920267</v>
+        <v>19220030050208</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>91</v>
@@ -3357,18 +3366,18 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920267</v>
+        <v>19220030050208</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>91</v>
@@ -3382,39 +3391,39 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920267</v>
+        <v>19220030050208</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920267</v>
+        <v>19220030050208</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>46</v>
@@ -3422,59 +3431,59 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920267</v>
+        <v>20330051920273</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920268</v>
+        <v>20330051920274</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
@@ -3482,16 +3491,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920268</v>
+        <v>20330051920274</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -3502,119 +3511,119 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920268</v>
+        <v>20330051920274</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920269</v>
+        <v>20330051920274</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920269</v>
+        <v>20330051920274</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920269</v>
+        <v>20330051920276</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920269</v>
+        <v>20330051920276</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920270</v>
+        <v>19330051920238</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>42</v>
@@ -3622,19 +3631,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
         <v>45</v>
@@ -3642,59 +3651,59 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920271</v>
+        <v>20330051920279</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
         <v>42</v>
@@ -3702,19 +3711,19 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920271</v>
+        <v>20330051920281</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
         <v>45</v>
@@ -3722,139 +3731,139 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920271</v>
+        <v>20330051920281</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920271</v>
+        <v>20330051920281</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920272</v>
+        <v>20330051920281</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920272</v>
+        <v>20330051920281</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920272</v>
+        <v>20330051920281</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920272</v>
+        <v>20330051920282</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
         <v>42</v>
@@ -3862,921 +3871,81 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19220030050208</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D54" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920273</v>
-      </c>
-      <c r="B55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920273</v>
-      </c>
-      <c r="B56" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920273</v>
-      </c>
-      <c r="B57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" t="s">
-        <v>98</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920273</v>
-      </c>
-      <c r="B58" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920274</v>
-      </c>
-      <c r="B59" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" t="s">
-        <v>80</v>
-      </c>
-      <c r="D59" t="s">
-        <v>99</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920274</v>
-      </c>
-      <c r="B60" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920274</v>
-      </c>
-      <c r="B61" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61" t="s">
-        <v>99</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920274</v>
-      </c>
-      <c r="B62" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" t="s">
-        <v>99</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920274</v>
-      </c>
-      <c r="B63" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63" t="s">
-        <v>99</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920274</v>
-      </c>
-      <c r="B64" t="s">
-        <v>63</v>
-      </c>
-      <c r="C64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64" t="s">
-        <v>99</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920274</v>
-      </c>
-      <c r="B65" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" t="s">
-        <v>99</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920276</v>
-      </c>
-      <c r="B66" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" t="s">
-        <v>100</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920276</v>
-      </c>
-      <c r="B67" t="s">
-        <v>64</v>
-      </c>
-      <c r="C67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67" t="s">
-        <v>100</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920276</v>
-      </c>
-      <c r="B68" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" t="s">
-        <v>81</v>
-      </c>
-      <c r="D68" t="s">
-        <v>100</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920276</v>
-      </c>
-      <c r="B69" t="s">
-        <v>64</v>
-      </c>
-      <c r="C69" t="s">
-        <v>81</v>
-      </c>
-      <c r="D69" t="s">
-        <v>100</v>
-      </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920238</v>
-      </c>
-      <c r="B70" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920238</v>
-      </c>
-      <c r="B71" t="s">
-        <v>65</v>
-      </c>
-      <c r="C71" t="s">
-        <v>82</v>
-      </c>
-      <c r="D71" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920238</v>
-      </c>
-      <c r="B72" t="s">
-        <v>65</v>
-      </c>
-      <c r="C72" t="s">
-        <v>82</v>
-      </c>
-      <c r="D72" t="s">
-        <v>101</v>
-      </c>
-      <c r="E72" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920278</v>
-      </c>
-      <c r="B73" t="s">
-        <v>66</v>
-      </c>
-      <c r="C73" t="s">
-        <v>83</v>
-      </c>
-      <c r="D73" t="s">
-        <v>102</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920278</v>
-      </c>
-      <c r="B74" t="s">
-        <v>66</v>
-      </c>
-      <c r="C74" t="s">
-        <v>83</v>
-      </c>
-      <c r="D74" t="s">
-        <v>102</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920278</v>
-      </c>
-      <c r="B75" t="s">
-        <v>66</v>
-      </c>
-      <c r="C75" t="s">
-        <v>83</v>
-      </c>
-      <c r="D75" t="s">
-        <v>102</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920278</v>
-      </c>
-      <c r="B76" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D76" t="s">
-        <v>102</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920278</v>
-      </c>
-      <c r="B77" t="s">
-        <v>66</v>
-      </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77" t="s">
-        <v>102</v>
-      </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920279</v>
-      </c>
-      <c r="B78" t="s">
-        <v>67</v>
-      </c>
-      <c r="C78" t="s">
-        <v>84</v>
-      </c>
-      <c r="D78" t="s">
-        <v>103</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920279</v>
-      </c>
-      <c r="B79" t="s">
-        <v>67</v>
-      </c>
-      <c r="C79" t="s">
-        <v>84</v>
-      </c>
-      <c r="D79" t="s">
-        <v>103</v>
-      </c>
-      <c r="E79" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920279</v>
-      </c>
-      <c r="B80" t="s">
-        <v>67</v>
-      </c>
-      <c r="C80" t="s">
-        <v>84</v>
-      </c>
-      <c r="D80" t="s">
-        <v>103</v>
-      </c>
-      <c r="E80" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920279</v>
-      </c>
-      <c r="B81" t="s">
-        <v>67</v>
-      </c>
-      <c r="C81" t="s">
-        <v>84</v>
-      </c>
-      <c r="D81" t="s">
-        <v>103</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920281</v>
-      </c>
-      <c r="B82" t="s">
-        <v>68</v>
-      </c>
-      <c r="C82" t="s">
-        <v>85</v>
-      </c>
-      <c r="D82" t="s">
-        <v>104</v>
-      </c>
-      <c r="E82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920281</v>
-      </c>
-      <c r="B83" t="s">
-        <v>68</v>
-      </c>
-      <c r="C83" t="s">
-        <v>85</v>
-      </c>
-      <c r="D83" t="s">
-        <v>104</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920281</v>
-      </c>
-      <c r="B84" t="s">
-        <v>68</v>
-      </c>
-      <c r="C84" t="s">
-        <v>85</v>
-      </c>
-      <c r="D84" t="s">
-        <v>104</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920281</v>
-      </c>
-      <c r="B85" t="s">
-        <v>68</v>
-      </c>
-      <c r="C85" t="s">
-        <v>85</v>
-      </c>
-      <c r="D85" t="s">
-        <v>104</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920281</v>
-      </c>
-      <c r="B86" t="s">
-        <v>68</v>
-      </c>
-      <c r="C86" t="s">
-        <v>85</v>
-      </c>
-      <c r="D86" t="s">
-        <v>104</v>
-      </c>
-      <c r="E86" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920281</v>
-      </c>
-      <c r="B87" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" t="s">
-        <v>85</v>
-      </c>
-      <c r="D87" t="s">
-        <v>104</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920281</v>
-      </c>
-      <c r="B88" t="s">
-        <v>68</v>
-      </c>
-      <c r="C88" t="s">
-        <v>85</v>
-      </c>
-      <c r="D88" t="s">
-        <v>104</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920282</v>
-      </c>
-      <c r="B89" t="s">
-        <v>69</v>
-      </c>
-      <c r="C89" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89" t="s">
-        <v>105</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920282</v>
-      </c>
-      <c r="B90" t="s">
-        <v>69</v>
-      </c>
-      <c r="C90" t="s">
-        <v>66</v>
-      </c>
-      <c r="D90" t="s">
-        <v>105</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920282</v>
-      </c>
-      <c r="B91" t="s">
-        <v>69</v>
-      </c>
-      <c r="C91" t="s">
-        <v>66</v>
-      </c>
-      <c r="D91" t="s">
-        <v>105</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920282</v>
-      </c>
-      <c r="B92" t="s">
-        <v>69</v>
-      </c>
-      <c r="C92" t="s">
-        <v>66</v>
-      </c>
-      <c r="D92" t="s">
-        <v>105</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920282</v>
-      </c>
-      <c r="B93" t="s">
-        <v>69</v>
-      </c>
-      <c r="C93" t="s">
-        <v>66</v>
-      </c>
-      <c r="D93" t="s">
-        <v>105</v>
-      </c>
-      <c r="E93" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920282</v>
-      </c>
-      <c r="B94" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94" t="s">
-        <v>105</v>
-      </c>
-      <c r="E94" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920282</v>
-      </c>
-      <c r="B95" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" t="s">
-        <v>66</v>
-      </c>
-      <c r="D95" t="s">
-        <v>105</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4816,84 +3985,84 @@
         <v>20330051920264</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920274</v>
+        <v>20330051920281</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920281</v>
+        <v>20330051920282</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920282</v>
+        <v>20330051920267</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4901,254 +4070,254 @@
         <v>19220030050208</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>20330051920261</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920314</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920269</v>
+        <v>20330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920270</v>
+        <v>20330051920271</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
         <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920272</v>
+        <v>20330051920269</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920273</v>
+        <v>20330051920272</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920276</v>
+        <v>20330051920273</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920279</v>
+        <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920260</v>
+        <v>20330051920279</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920262</v>
+        <v>20330051920260</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920268</v>
+        <v>20330051920262</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920238</v>
+        <v>20330051920268</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5158,7 +4327,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5188,6 +4357,282 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920270</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920271</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920271</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920276</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920276</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920279</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920269</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920272</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920273</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -158,12 +158,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,154 +188,154 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
   </si>
   <si>
     <t>MARTIN</t>
   </si>
   <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL ONAM</t>
   </si>
   <si>
-    <t>EUDY</t>
-  </si>
-  <si>
     <t>MIRANDA</t>
   </si>
   <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
     <t>IRVING JAIR</t>
   </si>
   <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
     <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
   </si>
 </sst>
 </file>
@@ -858,22 +858,22 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -900,7 +900,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -909,13 +909,13 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -941,28 +941,28 @@
         <v>-1</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1036,22 +1036,22 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1078,7 +1078,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1119,28 +1119,28 @@
         <v>-1</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1167,7 +1167,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>-1</v>
@@ -1182,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1193,43 +1193,43 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>-1</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1256,22 +1256,22 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>-1</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1282,7 +1282,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1291,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>7</v>
@@ -1303,16 +1303,16 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1345,16 +1345,16 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>-1</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1371,7 +1371,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -1380,19 +1380,19 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>7</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1401,13 +1401,13 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1443,13 +1443,13 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>7</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1481,22 +1481,22 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1529,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1564,28 +1564,28 @@
         <v>7</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1627,7 +1627,7 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1653,28 +1653,28 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1742,28 +1742,28 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1799,13 +1799,13 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1831,28 +1831,28 @@
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1888,13 +1888,13 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -1920,28 +1920,28 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1983,7 +1983,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -1994,16 +1994,16 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -2015,16 +2015,16 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2057,16 +2057,16 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>-1</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>-1</v>
@@ -2098,28 +2098,28 @@
         <v>7</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2161,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2187,25 +2187,25 @@
         <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2232,16 +2232,16 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2255,7 +2255,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2264,28 +2264,28 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2318,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -2327,7 +2327,7 @@
         <v>-1</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2353,28 +2353,28 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2407,7 +2407,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2416,7 +2416,7 @@
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2427,43 +2427,43 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>-1</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2490,22 +2490,22 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>-1</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2516,7 +2516,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -2525,19 +2525,19 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>-1</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2546,13 +2546,13 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2579,7 +2579,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>-1</v>
@@ -2588,13 +2588,13 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>-1</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2662,25 +2662,25 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>85</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2781,7 +2781,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2790,62 +2790,62 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>20</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
@@ -2854,25 +2854,25 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2882,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2917,10 +2917,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2937,36 +2937,36 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2977,50 +2977,50 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3031,56 +3031,56 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920264</v>
+        <v>20330051920267</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920264</v>
+        <v>20330051920270</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920264</v>
+        <v>20330051920271</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -3091,76 +3091,76 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920264</v>
+        <v>19220030050208</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
         <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920264</v>
+        <v>19220030050208</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
         <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920264</v>
+        <v>20330051920274</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -3171,782 +3171,162 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920267</v>
+        <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920269</v>
+        <v>20330051920281</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920270</v>
+        <v>20330051920281</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920270</v>
+        <v>20330051920282</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920271</v>
+        <v>20330051920282</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920271</v>
+        <v>20330051920282</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920272</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19220030050208</v>
-      </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19220030050208</v>
-      </c>
-      <c r="B25" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19220030050208</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19220030050208</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920273</v>
-      </c>
-      <c r="B28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920274</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920274</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920274</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920274</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920274</v>
-      </c>
-      <c r="B33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920274</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920276</v>
-      </c>
-      <c r="B35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920276</v>
-      </c>
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920238</v>
-      </c>
-      <c r="B37" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" t="s">
-        <v>95</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920278</v>
-      </c>
-      <c r="B38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920278</v>
-      </c>
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920278</v>
-      </c>
-      <c r="B40" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920279</v>
-      </c>
-      <c r="B41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920281</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" t="s">
-        <v>98</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920281</v>
-      </c>
-      <c r="B43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920281</v>
-      </c>
-      <c r="B44" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920281</v>
-      </c>
-      <c r="B45" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" t="s">
-        <v>98</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920281</v>
-      </c>
-      <c r="B46" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920281</v>
-      </c>
-      <c r="B47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" t="s">
-        <v>98</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920282</v>
-      </c>
-      <c r="B48" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" t="s">
-        <v>64</v>
-      </c>
-      <c r="D48" t="s">
-        <v>99</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920282</v>
-      </c>
-      <c r="B49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" t="s">
-        <v>64</v>
-      </c>
-      <c r="D49" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920282</v>
-      </c>
-      <c r="B50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" t="s">
-        <v>64</v>
-      </c>
-      <c r="D50" t="s">
-        <v>99</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920282</v>
-      </c>
-      <c r="B51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" t="s">
-        <v>99</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920282</v>
-      </c>
-      <c r="B52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" t="s">
-        <v>64</v>
-      </c>
-      <c r="D52" t="s">
-        <v>99</v>
-      </c>
-      <c r="E52" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920282</v>
-      </c>
-      <c r="B53" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D53" t="s">
-        <v>99</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3982,87 +3362,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920264</v>
+        <v>20330051920274</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920274</v>
+        <v>20330051920282</v>
       </c>
       <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920281</v>
+        <v>20330051920261</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920282</v>
+        <v>19330051920314</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920267</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4070,214 +3450,214 @@
         <v>19220030050208</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920261</v>
+        <v>20330051920281</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920314</v>
+        <v>20330051920267</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920270</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920270</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920276</v>
+        <v>20330051920278</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920269</v>
+        <v>20330051920260</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920272</v>
+        <v>20330051920262</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920273</v>
+        <v>20330051920268</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920238</v>
+        <v>20330051920269</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920279</v>
+        <v>20330051920272</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920260</v>
+        <v>20330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -4288,13 +3668,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920262</v>
+        <v>19330051920238</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -4305,13 +3685,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920268</v>
+        <v>20330051920279</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -4362,13 +3742,13 @@
         <v>20330051920270</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4385,13 +3765,13 @@
         <v>20330051920270</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4400,7 +3780,7 @@
         <v>42</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4408,13 +3788,13 @@
         <v>20330051920271</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4431,13 +3811,13 @@
         <v>20330051920271</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4446,21 +3826,21 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4474,16 +3854,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4497,22 +3877,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920279</v>
+        <v>20330051920276</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -4520,22 +3900,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920279</v>
+        <v>20330051920276</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4543,16 +3923,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920269</v>
+        <v>20330051920279</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4561,30 +3941,30 @@
         <v>42</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920272</v>
+        <v>20330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4592,13 +3972,13 @@
         <v>20330051920273</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4607,27 +3987,27 @@
         <v>42</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G13">
         <v>-1</v>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -152,10 +152,10 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -870,7 +870,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>5</v>
@@ -1048,7 +1048,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>6</v>
@@ -1090,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1315,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1493,7 +1493,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>7</v>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>10</v>
@@ -1624,7 +1624,7 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>5</v>
@@ -1760,7 +1760,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>5</v>
@@ -1802,7 +1802,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>5</v>
@@ -1849,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -1938,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -2158,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2202,7 +2202,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>7</v>
@@ -2238,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2371,7 +2371,7 @@
         <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -2413,7 +2413,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
         <v>5</v>
@@ -2717,66 +2717,66 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>63.16</v>
+        <v>55</v>
       </c>
       <c r="G4">
-        <v>36.84</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>63.16</v>
+      </c>
+      <c r="G5">
+        <v>36.84</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>65</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.5</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2926,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2966,7 +2966,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3006,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3146,7 +3146,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3226,7 +3226,7 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3246,7 +3246,7 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3286,7 +3286,7 @@
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3707,7 +3707,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3923,16 +3923,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920279</v>
+        <v>20330051920273</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3946,19 +3946,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920279</v>
+        <v>19330051920238</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -3969,47 +3969,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920273</v>
+        <v>20330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920278</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -149,15 +149,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -188,40 +188,106 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>LUNA</t>
   </si>
   <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>DIAZ</t>
@@ -230,31 +296,25 @@
     <t>CARRASCO</t>
   </si>
   <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
   </si>
   <si>
     <t>ELIAS ALONSO</t>
@@ -263,73 +323,13 @@
     <t>KARLA RENATA</t>
   </si>
   <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
   </si>
   <si>
     <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
   </si>
   <si>
     <t>IRVING JAIR</t>
@@ -861,7 +861,7 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1039,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1107,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -1170,7 +1170,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1259,7 +1259,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1285,7 +1285,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1306,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>10</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1484,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>10</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1641,7 +1641,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1730,7 +1730,7 @@
         <v>9</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1751,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -1793,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1840,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>10</v>
@@ -1882,7 +1882,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1929,7 +1929,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1997,7 +1997,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -2060,7 +2060,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2430,7 +2430,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2493,7 +2493,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2519,7 +2519,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2582,7 +2582,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>-1</v>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2694,83 +2694,83 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>55</v>
+        <v>63.16</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>36.84</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>63.16</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>36.84</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2882,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2917,33 +2917,33 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -2951,79 +2951,79 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920314</v>
+        <v>20330051920267</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920264</v>
+        <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920264</v>
+        <v>20330051920274</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -3031,39 +3031,39 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>43</v>
@@ -3071,19 +3071,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920271</v>
+        <v>20330051920281</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
@@ -3091,241 +3091,41 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19220030050208</v>
+        <v>20330051920282</v>
       </c>
       <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920274</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920274</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920274</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920276</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920278</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920281</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920281</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920282</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920282</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920282</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3365,16 +3165,16 @@
         <v>20330051920274</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3382,16 +3182,16 @@
         <v>20330051920282</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3402,13 +3202,13 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3419,13 +3219,13 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3436,61 +3236,61 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19220030050208</v>
+        <v>20330051920267</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920281</v>
+        <v>19220030050208</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3498,16 +3298,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920270</v>
+        <v>20330051920281</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
         <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3515,64 +3315,64 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920271</v>
+        <v>20330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920276</v>
+        <v>20330051920262</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920278</v>
+        <v>20330051920268</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920260</v>
+        <v>20330051920269</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
@@ -3583,13 +3383,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920262</v>
+        <v>20330051920270</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3600,13 +3400,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920268</v>
+        <v>20330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3617,13 +3417,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920269</v>
+        <v>20330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3634,13 +3434,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920272</v>
+        <v>20330051920273</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3651,13 +3451,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920273</v>
+        <v>20330051920276</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3671,10 +3471,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3688,10 +3488,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3707,7 +3507,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3742,36 +3542,36 @@
         <v>20330051920270</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920270</v>
+        <v>20330051920271</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3785,22 +3585,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920271</v>
+        <v>19220030050208</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -3808,16 +3608,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920271</v>
+        <v>20330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3831,162 +3631,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19220030050208</v>
+        <v>20330051920276</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19220030050208</v>
+        <v>19330051920238</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920276</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
       </c>
       <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920276</v>
-      </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920273</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920238</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920278</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1054,7 +1054,7 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1096,7 +1096,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1143,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1321,7 +1321,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1410,7 +1410,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1452,7 +1452,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1588,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1855,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1897,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1944,7 +1944,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2164,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2726,19 +2726,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>63.16</v>
+        <v>68.42</v>
       </c>
       <c r="G4">
-        <v>36.84</v>
+        <v>31.58</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3507,7 +3507,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3539,39 +3539,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920270</v>
+        <v>20330051920267</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920271</v>
+        <v>20330051920267</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3585,16 +3585,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19220030050208</v>
+        <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3603,21 +3603,21 @@
         <v>42</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920273</v>
+        <v>20330051920271</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3631,16 +3631,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920276</v>
+        <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -3649,27 +3649,27 @@
         <v>42</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920238</v>
+        <v>20330051920273</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3677,24 +3677,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
+        <v>20330051920276</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920238</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
         <v>20330051920278</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>67</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>75</v>
       </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>43</v>
       </c>
-      <c r="G8">
+      <c r="G10">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -152,16 +152,16 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>NC</t>
@@ -879,16 +879,16 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -897,10 +897,10 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -950,7 +950,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -965,19 +965,19 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -989,7 +989,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -998,7 +998,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>-1</v>
@@ -1057,16 +1057,16 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1146,16 +1146,16 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1164,13 +1164,13 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1185,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1217,7 +1217,7 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -1232,19 +1232,19 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1256,7 +1256,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1265,7 +1265,7 @@
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>-1</v>
@@ -1324,16 +1324,16 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1342,13 +1342,13 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1363,7 +1363,7 @@
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1395,7 +1395,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1413,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1422,7 +1422,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1431,19 +1431,19 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>7</v>
@@ -1452,7 +1452,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1502,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1520,13 +1520,13 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1541,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1591,16 +1591,16 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1609,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1630,7 +1630,7 @@
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1677,19 +1677,19 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1698,7 +1698,7 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1710,7 +1710,7 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1719,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1769,16 +1769,16 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1787,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1799,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1858,16 +1858,16 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1876,7 +1876,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1947,16 +1947,16 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1965,10 +1965,10 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2018,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -2033,19 +2033,19 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2054,19 +2054,19 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2125,16 +2125,16 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2143,13 +2143,13 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2193,7 +2193,7 @@
         <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>9</v>
@@ -2208,16 +2208,16 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2229,7 +2229,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2273,7 +2273,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>10</v>
@@ -2288,19 +2288,19 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2309,13 +2309,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2330,7 +2330,7 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2362,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2377,19 +2377,19 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2398,13 +2398,13 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2419,7 +2419,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2451,7 +2451,7 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -2466,19 +2466,19 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2490,7 +2490,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2499,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>-1</v>
@@ -2540,7 +2540,7 @@
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2555,19 +2555,19 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2579,7 +2579,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2588,7 +2588,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>-1</v>
@@ -2717,28 +2717,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>68.42</v>
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>31.58</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2749,28 +2749,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>78.95</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>21.05</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2790,51 +2790,51 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>90</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>20</v>
       </c>
       <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>80</v>
+      </c>
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>47</v>
@@ -2854,25 +2854,25 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2986,7 +2986,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3126,7 +3126,7 @@
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3507,7 +3507,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3539,22 +3539,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920267</v>
+        <v>19330051920314</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -3562,16 +3562,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920267</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3585,39 +3585,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920274</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920271</v>
+        <v>20330051920274</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3626,44 +3626,44 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19220030050208</v>
+        <v>20330051920279</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920273</v>
+        <v>20330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3677,16 +3677,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920276</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920238</v>
+        <v>20330051920271</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3723,24 +3723,116 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>19220030050208</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920273</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920276</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>20330051920278</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D14" t="s">
         <v>75</v>
       </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
         <v>43</v>
       </c>
-      <c r="G10">
+      <c r="G14">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -185,130 +185,130 @@
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>ANDRADE</t>
   </si>
   <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
   </si>
   <si>
     <t>JESUS HUMBERTO</t>
@@ -885,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>9</v>
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -995,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>6</v>
@@ -1063,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -1152,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1330,7 +1330,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1377,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1398,7 +1398,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1419,7 +1419,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1440,7 +1440,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1508,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1686,7 +1686,7 @@
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -1775,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1864,7 +1864,7 @@
         <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1953,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>9</v>
@@ -2042,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -2131,7 +2131,7 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -2214,7 +2214,7 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>9</v>
@@ -2232,7 +2232,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2297,7 +2297,7 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2386,7 +2386,7 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>5</v>
@@ -2496,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2522,7 +2522,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2543,7 +2543,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -2564,7 +2564,7 @@
         <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2854,25 +2854,25 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>8.4</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>90</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2882,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2917,10 +2917,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2937,10 +2937,10 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2957,10 +2957,10 @@
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -2971,42 +2971,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920267</v>
+        <v>19220030050208</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19220030050208</v>
+        <v>20330051920274</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3014,53 +3014,53 @@
         <v>20330051920274</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920274</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920278</v>
+        <v>20330051920281</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3071,62 +3071,22 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920281</v>
+        <v>20330051920282</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920282</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920282</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3165,13 +3125,13 @@
         <v>20330051920274</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3179,33 +3139,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920282</v>
+        <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920261</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
         <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3213,16 +3173,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3230,16 +3190,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920264</v>
+        <v>19220030050208</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -3247,13 +3207,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>72</v>
@@ -3264,13 +3224,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19220030050208</v>
+        <v>20330051920281</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
         <v>73</v>
@@ -3281,16 +3241,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920278</v>
+        <v>20330051920282</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3298,30 +3258,30 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920281</v>
+        <v>20330051920260</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920260</v>
+        <v>20330051920262</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -3332,13 +3292,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920262</v>
+        <v>20330051920267</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -3352,10 +3312,10 @@
         <v>20330051920268</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -3369,10 +3329,10 @@
         <v>20330051920269</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
@@ -3386,10 +3346,10 @@
         <v>20330051920270</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3403,10 +3363,10 @@
         <v>20330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3420,10 +3380,10 @@
         <v>20330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3437,10 +3397,10 @@
         <v>20330051920273</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3454,10 +3414,10 @@
         <v>20330051920276</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3471,10 +3431,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3488,10 +3448,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3545,10 +3505,10 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3568,10 +3528,10 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3588,13 +3548,13 @@
         <v>20330051920274</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -3611,13 +3571,13 @@
         <v>20330051920274</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3634,10 +3594,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
@@ -3657,10 +3617,10 @@
         <v>20330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
         <v>105</v>
@@ -3680,10 +3640,10 @@
         <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
         <v>99</v>
@@ -3703,10 +3663,10 @@
         <v>20330051920271</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -3726,13 +3686,13 @@
         <v>19220030050208</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -3749,10 +3709,10 @@
         <v>20330051920273</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
         <v>102</v>
@@ -3772,10 +3732,10 @@
         <v>20330051920276</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>103</v>
@@ -3795,10 +3755,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>104</v>
@@ -3818,13 +3778,13 @@
         <v>20330051920278</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>

--- a/grupos/4APV - Estadisticos 20212.xlsx
+++ b/grupos/4APV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="106">
   <si>
     <t>Materia</t>
   </si>
@@ -176,30 +176,63 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>BENITEZ</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>DE LUNA</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>TELLEZ</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -209,133 +242,100 @@
     <t>GARNICA</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
     <t>CORDOVA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
     <t>LEONARDO GAEL</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
     <t>EUDY</t>
   </si>
   <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
     <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
   </si>
 </sst>
 </file>
@@ -891,10 +891,10 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -938,7 +938,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -959,7 +959,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -980,13 +980,13 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1001,7 +1001,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>5</v>
@@ -1069,10 +1069,10 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1116,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1137,7 +1137,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1158,10 +1158,10 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1179,7 +1179,7 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1205,7 +1205,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1226,7 +1226,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -1247,13 +1247,13 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1297,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1318,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1336,10 +1336,10 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>10</v>
@@ -1360,7 +1360,7 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1404,7 +1404,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>4</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1425,10 +1425,10 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1446,7 +1446,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1514,10 +1514,10 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1535,10 +1535,10 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1603,10 +1603,10 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1624,7 +1624,7 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>10</v>
@@ -1692,10 +1692,10 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1713,7 +1713,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1781,10 +1781,10 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1802,10 +1802,10 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1870,10 +1870,10 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1894,7 +1894,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -1959,10 +1959,10 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1980,10 +1980,10 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>8</v>
@@ -2006,10 +2006,10 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -2027,10 +2027,10 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2048,10 +2048,10 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2069,10 +2069,10 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2137,10 +2137,10 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2161,7 +2161,7 @@
         <v>9</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2220,10 +2220,10 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2238,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2261,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2282,7 +2282,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>6</v>
@@ -2303,10 +2303,10 @@
         <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2324,10 +2324,10 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2392,10 +2392,10 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2439,7 +2439,7 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2460,7 +2460,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2481,13 +2481,13 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2502,7 +2502,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2528,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2549,7 +2549,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>5</v>
@@ -2570,13 +2570,13 @@
         <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2591,7 +2591,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB23">
         <v>5</v>
@@ -2662,25 +2662,25 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2694,25 +2694,25 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2882,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2907,186 +2907,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920261</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920314</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920264</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19220030050208</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920274</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920274</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920278</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920281</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920282</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3122,19 +2942,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920274</v>
+        <v>20330051920260</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3142,16 +2962,16 @@
         <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3159,112 +2979,112 @@
         <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920264</v>
+        <v>20330051920262</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19220030050208</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920278</v>
+        <v>20330051920267</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920281</v>
+        <v>20330051920268</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920282</v>
+        <v>20330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920260</v>
+        <v>20330051920270</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>94</v>
@@ -3275,13 +3095,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920262</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -3292,13 +3112,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920267</v>
+        <v>20330051920272</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -3309,13 +3129,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920268</v>
+        <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -3326,13 +3146,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920269</v>
+        <v>20330051920273</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
@@ -3343,13 +3163,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920270</v>
+        <v>20330051920274</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3360,13 +3180,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3377,13 +3197,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920272</v>
+        <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3394,13 +3214,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920273</v>
+        <v>20330051920278</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3411,13 +3231,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920276</v>
+        <v>20330051920279</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3428,13 +3248,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920238</v>
+        <v>20330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3445,13 +3265,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920279</v>
+        <v>20330051920282</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3467,7 +3287,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3499,16 +3319,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>20330051920279</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3517,21 +3337,21 @@
         <v>43</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920279</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3545,39 +3365,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920274</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920274</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3586,27 +3406,27 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920279</v>
+        <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3614,16 +3434,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920279</v>
+        <v>20330051920274</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3633,167 +3453,6 @@
       </c>
       <c r="G7">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920270</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920271</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19220030050208</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920273</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920276</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920238</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920278</v>
-      </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
